--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit pas. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter. Dimitri dit : ce n'est pas gentil. Il ramasse le gant. Il le tend. Lila le remet. La maîtresse s'approche. Tom dit : pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire. Dimitri se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Maman entend. Maman dit : tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Dimitri serre la main de maman.</t>
+          <t>Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit pas. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il ramasse le gant. Il le tend. Lila le remet. La maîtresse s'approche. Pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire. Dimitri se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Dimitri serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit pas. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter.
+enfant-m|Ce n'est pas gentil. Il ramasse le gant. Il le tend.
+narrateur|Lila le remet. La maîtresse s'approche.
+copain|Pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire.
+narrateur|Dimitri se souvient. Il ne rit pas. Il ne répète pas.
+narrateur|Ce n'est pas gentil. Maman entend.
+maman|Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
+narrateur|Ce n'est pas gentil.
+narrateur|Dimitri serre la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1496,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rit. Que fait Dimitri ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1525,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dimitri n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.</t>
+          <t>Dimitri n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1667,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri n'a pas ri. Il n'a pas répété. Il
+enfant-f|Ce n'est pas gentil. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri range son cartable. Maman marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Dimitri serre la main de maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Tom rit. Que fait Dimitri ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
 enfant-f|Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Dimitri range son cartable. Maman marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dimitri ne rit pas, deux fois</t>
+          <t>Le gant et le livre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un gant glisse à l'école, puis un livre à la maison. Aniss n'est pas là pour rire. Il aide, deux fois. Papa l'écoute.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit pas. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il ramasse le gant. Il le tend. Lila le remet. La maîtresse s'approche. Pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire. Dimitri se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Dimitri serre la main de maman.</t>
+          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit pas. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter.
-enfant-m|Ce n'est pas gentil. Il ramasse le gant. Il le tend.
-narrateur|Lila le remet. La maîtresse s'approche.
-copain|Pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire.
-narrateur|Dimitri se souvient. Il ne rit pas. Il ne répète pas.
-narrateur|Ce n'est pas gentil. Maman entend.
-maman|Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
-narrateur|Ce n'est pas gentil.
-narrateur|Dimitri serre la main de maman.</t>
+          <t>narrateur|Les cartables tapent doucement contre les casiers.
+narrateur|L'escalier en bois craque, une marche après l'autre.
+narrateur|Ça sent le pain du goûter, tout loin.
+narrateur|Une lanière de cuir claque, puis plus.
+papa|Ton gant vert est dans la poche, Aniss.
+papa|Tu as entendu l'escalier ?
+enfant-m|Oui, papa.
+enfant-m|Il parle un peu.
+papa|On accroche le cartable.
+papa|Bravo.
+papa|Je reviens te chercher.
+enfant-m|D'accord, papa.
+narrateur|En ce moment, la classe range les cartables.
+narrateur|Nina tient un gant rose.
+narrateur|Le gant glisse.
+narrateur|Il tombe près du casier.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Aniss n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il ramasse le gant.
+narrateur|Le tissu est doux, un peu froid.
+narrateur|Il le tend.
+copine|Merci, Aniss.
+narrateur|Nina remet le gant.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-m|On aide.
+narrateur|Plus tard, à la maison, le tapis est doux.
+narrateur|Ça sent le pain, tout près.
+papa|On pose le livre ici, Aniss.
+papa|Les pages sont bien à plat.
+enfant-m|D'accord, papa.
+narrateur|Un livre glisse.
+narrateur|Il tombe près du tapis.
+narrateur|Les pages font un bruit de papier.
+narrateur|Encore un petit rire, tout court.
+narrateur|Aniss se souvient.
+narrateur|Il n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il ramasse le livre.
+narrateur|Il le tend à Nina.
+copine|Merci.
+narrateur|Papa entend.
+papa|Tu as bien fait.
+papa|Même leçon, autre lieu.
+papa|Il ne faut pas rire.
+papa|Il ne faut pas répéter.
+papa|Ce n'est pas gentil.
+papa|C'est du bon travail.
+papa|Tu as senti le pain, tout à l'heure ?
+enfant-m|Oui, papa.
+papa|On en prendra une tranche.
+narrateur|Aniss serre la main de papa.
+narrateur|Le livre est refermé, sur le tapis.
+narrateur|L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1348,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom rit. Que fait Dimitri ?</t>
+          <t>Un camarade rit. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom rit. Que fait Dimitri ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Aniss ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dimitri n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
+          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,8 +1740,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri n'a pas ri. Il n'a pas répété. Il
-enfant-f|Ce n'est pas gentil. Maman est là.</t>
+          <t>narrateur|Aniss n'a pas ri.
+narrateur|Il n'a pas répété.
+narrateur|Il a dit : ce n'est pas gentil.
+narrateur|À l'école, puis à la maison.
+papa|Tu as ramassé le gant.
+papa|Puis le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+enfant-m|On aide.
+enfant-m|Deux fois.
+papa|Oui.
+papa|Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dimitri range son cartable. Maman marche à côté.</t>
+          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1915,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri range son cartable. Maman marche à côté.</t>
+          <t>narrateur|Aniss range son cartable près de la porte.
+narrateur|Le zip fait un petit bruit.
+papa|Tu as fini de ranger ?
+enfant-m|Oui, papa.
+papa|Le livre de Nina est refermé.
+papa|On prend le pain ?
+enfant-m|Oui.
+narrateur|Papa marche à côté.
+narrateur|Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Tu as fait du bon travail. Le livre reste fermé, bien à plat. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2091,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai ramassé.
+enfant-m|À l'école, puis à la maison.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le livre reste fermé, bien à plat.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
+          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri est à l'école. La classe range les cartables. Lila fait tomber son gant. Tom commence à rire. Le rire est court. Dimitri ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Dimitri ne répète pas. Il ne faut pas répéter. Dimitri dit : ce n'est pas gentil. Il ramasse le gant. Il le tend. Lila le remet. La maîtresse s'approche. Tom dit : pardon. Plus tard, à la maison, un livre glisse. Encore un petit rire. Dimitri se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Maman entend. Maman dit : tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Dimitri serre la main de maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 papa|Il ne faut pas rire.
 papa|Il ne faut pas répéter.
 papa|Ce n'est pas gentil.
-papa|C'est du bon travail.
 papa|Tu as senti le pain, tout à l'heure ?
 enfant-m|Oui, papa.
 papa|On en prendra une tranche.
@@ -1386,7 +1385,6 @@
 narrateur|L'escalier ne craque plus.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1416,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom rit. Que fait Dimitri ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1569,6 @@
 narrateur|Que fait Aniss ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,14 +1744,12 @@
 papa|Tu as ramassé le gant.
 papa|Puis le livre.
 papa|Bravo.
-papa|C'est du bon travail.
 enfant-m|On aide.
 enfant-m|Deux fois.
 papa|Oui.
 papa|Même geste, autre lieu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri range son cartable. Maman marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,7 +1921,6 @@
 narrateur|Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Tu as fait du bon travail. Le livre reste fermé, bien à plat. L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le livre reste fermé, bien à plat.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le livre reste fermé, bien à plat.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,12 +2088,9 @@
           <t>enfant-m|J'ai ramassé.
 enfant-m|À l'école, puis à la maison.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le livre reste fermé, bien à plat.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le livre reste fermé, bien à plat.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2118,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dimitri, Lila, Tom, maman</t>
+          <t>Aniss, Nina, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le gant et le livre</t>
+          <t>Le gant près de l'escalier</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis maison</t>
+          <t>école, casiers, puis tapis et pain à la maison</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un gant glisse à l'école, puis un livre à la maison. Aniss n'est pas là pour rire. Il aide, deux fois. Papa l'écoute.</t>
+          <t>Aniss veut lire avec Nina, puis goûter le pain. Le gant rose tombe. Un rire commence. Nina a le visage triste. Il s'arrête, tend le gant. À la maison, le livre glisse. Même geste vécu. Ils lisent. Le pain sent chaud.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
+          <t>L'escalier en bois craque, une marche après l'autre. Les cartables tapent doucement contre les casiers. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Je reviens te chercher. D'accord, papa. Papa part vers la porte. En ce moment, Nina tient un gant rose. Le tissu est doux, un peu froid. On le met près du casier ? Oui. Le gant glisse. Il tombe près du casier. Un petit rire commence dans la gorge d'Aniss. Nina baisse les yeux. Sa bouche devient toute petite. Le gant reste par terre. Aniss referme la bouche. Le rire ne sort plus. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. Il est chaud, maintenant ? Un peu. La maîtresse s'approche. Votre gant est remis ? Oui. Vous pouvez aller lire, alors. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. On lit, Nina ? Oui. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Un petit rire recommence, tout court. Nina regarde le livre. Ses joues baissent. Aniss referme encore la bouche. Il ramasse le livre. Il le tend à Nina. Merci. On lit la page des oiseaux ? Oui. Les pages restent à plat, sur le tapis. Vous lisez ensemble ? Oui, papa. Bravo, Aniss. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche ? Oui. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les cartables tapent doucement contre les casiers. L'escalier en bois craque, une marche après l'autre. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les cartables. Nina tient un gant rose. Le gant glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Aniss n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. D'accord, papa. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Encore un petit rire, tout court. Aniss se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le livre. Il le tend à Nina. Merci. Papa entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
+          <t>L'escalier en bois craque, une marche après l'autre. Les cartables tapent doucement contre les casiers. Ça sent le pain du goûter, tout loin. Une lanière de cuir claque, puis plus. Ton gant vert est dans la poche, Aniss. Tu as entendu l'escalier ? Oui, papa. Il parle un peu. On accroche le cartable. Je reviens te chercher. D'accord, papa. Papa part vers la porte. En ce moment, Nina tient un gant rose. Le tissu est doux, un peu froid. On le met près du casier ? Oui. Le gant glisse. Il tombe près du casier. Un petit rire commence dans la gorge d'Aniss. Nina baisse les yeux. Sa bouche devient toute petite. Le gant reste par terre. Aniss referme la bouche. Le rire ne sort plus. Il ramasse le gant. Le tissu est doux, un peu froid. Il le tend. Merci, Aniss. Nina remet le gant. Il est chaud, maintenant ? Un peu. La maîtresse s'approche. Votre gant est remis ? Oui. Vous pouvez aller lire, alors. Plus tard, à la maison, le tapis est doux. Ça sent le pain, tout près. On pose le livre ici, Aniss. Les pages sont bien à plat. On lit, Nina ? Oui. Un livre glisse. Il tombe près du tapis. Les pages font un bruit de papier. Un petit rire recommence, tout court. Nina regarde le livre. Ses joues baissent. Aniss referme encore la bouche. Il ramasse le livre. Il le tend à Nina. Merci. On lit la page des oiseaux ? Oui. Les pages restent à plat, sur le tapis. Vous lisez ensemble ? Oui, papa. Bravo, Aniss. Tu as senti le pain, tout à l'heure ? Oui, papa. On en prendra une tranche ? Oui. Aniss serre la main de papa. Le livre est refermé, sur le tapis. L'escalier ne craque plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,8 +1324,8 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les cartables tapent doucement contre les casiers.
-narrateur|L'escalier en bois craque, une marche après l'autre.
+          <t>narrateur|L'escalier en bois craque, une marche après l'autre.
+narrateur|Les cartables tapent doucement contre les casiers.
 narrateur|Ça sent le pain du goûter, tout loin.
 narrateur|Une lanière de cuir claque, puis plus.
 papa|Ton gant vert est dans la poche, Aniss.
@@ -1333,53 +1333,58 @@
 enfant-m|Oui, papa.
 enfant-m|Il parle un peu.
 papa|On accroche le cartable.
-papa|Bravo.
 papa|Je reviens te chercher.
 enfant-m|D'accord, papa.
-narrateur|En ce moment, la classe range les cartables.
-narrateur|Nina tient un gant rose.
+narrateur|Papa part vers la porte.
+narrateur|En ce moment, Nina tient un gant rose.
+narrateur|Le tissu est doux, un peu froid.
+enfant-m|On le met près du casier ?
+copine|Oui.
 narrateur|Le gant glisse.
 narrateur|Il tombe près du casier.
-narrateur|Un camarade commence un petit rire.
-narrateur|Le rire est court.
-narrateur|Aniss n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
+narrateur|Un petit rire commence dans la gorge d'Aniss.
+narrateur|Nina baisse les yeux.
+narrateur|Sa bouche devient toute petite.
+narrateur|Le gant reste par terre.
+narrateur|Aniss referme la bouche.
+narrateur|Le rire ne sort plus.
 narrateur|Il ramasse le gant.
 narrateur|Le tissu est doux, un peu froid.
 narrateur|Il le tend.
 copine|Merci, Aniss.
 narrateur|Nina remet le gant.
+enfant-m|Il est chaud, maintenant ?
+copine|Un peu.
 narrateur|La maîtresse s'approche.
-maitresse|On aide.
-maitresse|On n'est pas là pour rire.
-maitresse|On n'est pas là pour répéter.
-enfant-m|On aide.
+maitresse|Votre gant est remis ?
+copine|Oui.
+maitresse|Vous pouvez aller lire, alors.
 narrateur|Plus tard, à la maison, le tapis est doux.
 narrateur|Ça sent le pain, tout près.
 papa|On pose le livre ici, Aniss.
 papa|Les pages sont bien à plat.
-enfant-m|D'accord, papa.
+enfant-m|On lit, Nina ?
+copine|Oui.
 narrateur|Un livre glisse.
 narrateur|Il tombe près du tapis.
 narrateur|Les pages font un bruit de papier.
-narrateur|Encore un petit rire, tout court.
-narrateur|Aniss se souvient.
-narrateur|Il n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
+narrateur|Un petit rire recommence, tout court.
+narrateur|Nina regarde le livre.
+narrateur|Ses joues baissent.
+narrateur|Aniss referme encore la bouche.
 narrateur|Il ramasse le livre.
 narrateur|Il le tend à Nina.
 copine|Merci.
-narrateur|Papa entend.
-papa|Tu as bien fait.
-papa|Même leçon, autre lieu.
-papa|Il ne faut pas rire.
-papa|Il ne faut pas répéter.
-papa|Ce n'est pas gentil.
+enfant-m|On lit la page des oiseaux ?
+copine|Oui.
+narrateur|Les pages restent à plat, sur le tapis.
+papa|Vous lisez ensemble ?
+enfant-m|Oui, papa.
+papa|Bravo, Aniss.
 papa|Tu as senti le pain, tout à l'heure ?
 enfant-m|Oui, papa.
-papa|On en prendra une tranche.
+papa|On en prendra une tranche ?
+enfant-m|Oui.
 narrateur|Aniss serre la main de papa.
 narrateur|Le livre est refermé, sur le tapis.
 narrateur|L'escalier ne craque plus.</t>
@@ -1429,7 +1434,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | pas gentil | ne pas rire | pas répéter</t>
+          <t>pas rire | pas gentil | ne pas rire | pas répéter | ramasse | il ramasse | il tend</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il ne rit pas. Il dit que ce n'est pas gentil. Que fait Dimitri ?</t>
+          <t>Aniss voit le visage de Nina. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1486,14 +1491,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1593,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Aniss a vu le visage de Nina. Le rire s'est arrêté. Il a tendu le gant, puis le livre. Bravo. Vous avez lu, et le pain attend. La page des oiseaux. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aniss n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le gant. Puis le livre. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Aniss a vu le visage de Nina. Le rire s'est arrêté. Il a tendu le gant, puis le livre. Bravo. Vous avez lu, et le pain attend. La page des oiseaux. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1661,7 +1666,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1737,17 +1742,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss n'a pas ri.
-narrateur|Il n'a pas répété.
-narrateur|Il a dit : ce n'est pas gentil.
-narrateur|À l'école, puis à la maison.
-papa|Tu as ramassé le gant.
-papa|Puis le livre.
+          <t>narrateur|Aniss a vu le visage de Nina.
+narrateur|Le rire s'est arrêté.
+narrateur|Il a tendu le gant, puis le livre.
 papa|Bravo.
-enfant-m|On aide.
-enfant-m|Deux fois.
-papa|Oui.
-papa|Même geste, autre lieu.</t>
+papa|Vous avez lu, et le pain attend.
+enfant-m|La page des oiseaux.
+papa|Oui.</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. Ça sent le pain, tout près, maintenant.</t>
+          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. La tranche est encore tiède ? Oui, un peu. Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. Ça sent le pain, tout près, maintenant.</t>
+          <t>Aniss range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le livre de Nina est refermé. On prend le pain ? Oui. Papa marche à côté. La tranche est encore tiède ? Oui, un peu. Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1842,7 +1843,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1918,6 +1919,8 @@
 papa|On prend le pain ?
 enfant-m|Oui.
 narrateur|Papa marche à côté.
+papa|La tranche est encore tiède ?
+enfant-m|Oui, un peu.
 narrateur|Ça sent le pain, tout près, maintenant.</t>
         </is>
       </c>
@@ -1945,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le livre reste fermé, bien à plat.</t>
+          <t>On a lu. Puis le pain. Bravo. Le livre reste fermé, bien à plat.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le livre reste fermé, bien à plat.</t>
+          <t>On a lu. Puis le pain. Bravo. Le livre reste fermé, bien à plat.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2013,7 +2016,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2085,8 +2088,8 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai ramassé.
-enfant-m|À l'école, puis à la maison.
+          <t>enfant-m|On a lu.
+enfant-m|Puis le pain.
 papa|Bravo.
 narrateur|Le livre reste fermé, bien à plat.</t>
         </is>
@@ -2109,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2162,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
